--- a/lesson-1-4-visualizing-distributions/skyline_distributions.xlsx
+++ b/lesson-1-4-visualizing-distributions/skyline_distributions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenyaharvey/northstar-coursework/module-01-foundations-of-analytics-and-statistics/lesson-1-4-visualizing-distributions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5A7A63-19DE-D243-9C04-0329B4DB6C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A797B6-CC7D-BA4B-8772-44D3FE19B924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" activeTab="4" xr2:uid="{F6A83419-28F0-A644-8AD6-2D70765D3544}"/>
   </bookViews>
@@ -17,21 +17,16 @@
     <sheet name="short_reflection" sheetId="6" r:id="rId2"/>
     <sheet name="hours_studied_box_plot" sheetId="5" r:id="rId3"/>
     <sheet name="enrollment_year" sheetId="4" r:id="rId4"/>
-    <sheet name="skyline_enrollments" sheetId="1" r:id="rId5"/>
-    <sheet name="hours_studied_by_course" sheetId="3" r:id="rId6"/>
+    <sheet name="distribution_notes" sheetId="7" r:id="rId5"/>
+    <sheet name="skyline_enrollments" sheetId="1" r:id="rId6"/>
+    <sheet name="hours_studied_by_course" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">skyline_enrollments!$E$1</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">skyline_enrollments!$E$2:$E$101</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">skyline_enrollments!$E$2:$E$101</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">skyline_enrollments!$E$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">skyline_enrollments!$E$2:$E$101</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">skyline_enrollments!$E$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">skyline_enrollments!$E$2:$E$101</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">skyline_enrollments!$E$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">skyline_enrollments!$E$2:$E$101</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">skyline_enrollments!$B$2:$B$101</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">skyline_enrollments!$E$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">skyline_enrollments!$B$2:$B$101</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">skyline_enrollments!$E$1</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">skyline_enrollments!$E$2:$E$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -1446,7 +1441,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -1459,6 +1454,13 @@
           </a:r>
         </a:p>
       </cx:txPr>
+      <cx:extLst>
+        <cx:ext uri="ext:featex">
+          <cx:featureExtension feature="mp" drop="onModelChange">
+            <cx:offset top="0.097222223877906799" left="-0.041666656732559204"/>
+          </cx:featureExtension>
+        </cx:ext>
+      </cx:extLst>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
@@ -1509,6 +1511,13 @@
               </a:r>
             </a:p>
           </cx:txPr>
+          <cx:extLst>
+            <cx:ext uri="ext:featex">
+              <cx:featureExtension feature="mp" drop="onModelChange">
+                <cx:offset left="0.013889982365071774"/>
+              </cx:featureExtension>
+            </cx:ext>
+          </cx:extLst>
         </cx:title>
         <cx:majorGridlines/>
         <cx:tickLabels/>
@@ -1523,10 +1532,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.8</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.10</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1534,7 +1543,7 @@
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
         <cx:txData>
-          <cx:v>Hours Studied by Course</cx:v>
+          <cx:v>Hours Studied by Course: Box Plot</cx:v>
         </cx:txData>
       </cx:tx>
       <cx:txPr>
@@ -1545,7 +1554,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -1554,7 +1563,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
             </a:rPr>
-            <a:t>Hours Studied by Course</a:t>
+            <a:t>Hours Studied by Course: Box Plot</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -1564,7 +1573,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000000-C9F1-DC41-BEC9-09DC6757DBC0}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.9</cx:f>
+              <cx:f>_xlchart.v1.3</cx:f>
               <cx:v>Hours_studied</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2996,6 +3005,215 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8E5251D-EC9C-1DF6-C746-4AD8469CE141}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3314700" y="2755900"/>
+          <a:ext cx="10566400" cy="6921500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1"/>
+            <a:t>Distribution Notes</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="2000" b="1"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>1. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>hours_studied</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>distribution shape:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>The distribution shows a staircase pattern leading up to two tall points: bars ranging from 28-30, which are all similar, all at a lower level, before rising up to a tallest bar at 31. The same pattern repeats itself ranging from 32-34, which are all similar as well before jumping again to the next tallest bar at 35. Overall, a symmetric bell-like shape has been created, with a chunk of the data clustering from low-to-mid 30s and both leveling out evenly on either side.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>2. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>enrollment_year</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>distribution shape:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>This distribution is right-skewed, with one peak centered at 2023. After 2023, values (26 → 20 → 18 → 15) extend further out and decline gradually, while the year before 2023 seems to drop off more quickly by </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t>comparison.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>3. Box plot vs. histogram (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>hours_studied</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>):</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>The mean told me that students study 30.06 hours. Based on the histogram, there are two peaks with a dip in between. The mean does not show that there are two clusters.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1"/>
+            <a:t>4. Box plot grouped by course:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>The box plot grouped by course shows that the means for Statistics 101, Tableau Fundamentals, and SQL Basics are roughly the same, centered around 30. Python for Beginners and Intro to Analytics have means that are close to each other as well. The medians are roughly the same across all courses. The spread is also roughly the same across all courses.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="2000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3560,6 +3778,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EA8808-4E74-504F-B3B4-844D6CFFE8BD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E062A01B-319A-2146-9114-9452F7DCB581}">
   <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5596,7 +5824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EDAD38-BA95-734C-B6B3-200DDD0A5462}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
